--- a/data/v2/part24_labeled_dataset.xlsx
+++ b/data/v2/part24_labeled_dataset.xlsx
@@ -18,7 +18,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
   <fonts count="14">
     <font>
       <name val="Calibri"/>
@@ -163,7 +165,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -251,6 +253,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1515,13 +1520,39 @@
           <t>019</t>
         </is>
       </c>
-      <c r="B20" s="26" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="26" t="n"/>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>Pitch a faster way to write compact conditional logic in Python without sacrificing readability.</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="n">
+        <v>43752</v>
+      </c>
+      <c r="F20" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0572/</t>
+        </is>
+      </c>
+      <c r="G20" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H20" s="26" t="inlineStr">
+        <is>
+          <t>PEP 572; implemented in Python 3.8. Human pre-label: Yes (syntax ergonomics vs added language complexity).</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="16">
       <c r="A21" s="22" t="inlineStr">
@@ -1529,13 +1560,39 @@
           <t>020</t>
         </is>
       </c>
-      <c r="B21" s="26" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="26" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="26" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="26" t="n"/>
+      <c r="B21" s="26" t="inlineStr">
+        <is>
+          <t>Pitch a standard way to write built-in generic collections such as list[str] and dict[str, int] for static typing.</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D21" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>44109</v>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0585/</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H21" s="26" t="inlineStr">
+        <is>
+          <t>PEP 585; implemented in Python 3.9. Human pre-label: No.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="16">
       <c r="A22" s="22" t="inlineStr">
@@ -1543,13 +1600,39 @@
           <t>021</t>
         </is>
       </c>
-      <c r="B22" s="26" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="26" t="n"/>
-      <c r="G22" s="26" t="n"/>
-      <c r="H22" s="26" t="n"/>
+      <c r="B22" s="26" t="inlineStr">
+        <is>
+          <t>Pitch a concise union-type syntax using X | Y instead of verbose typing.Union expressions.</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D22" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E22" s="30" t="n">
+        <v>44473</v>
+      </c>
+      <c r="F22" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0604/</t>
+        </is>
+      </c>
+      <c r="G22" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H22" s="26" t="inlineStr">
+        <is>
+          <t>PEP 604; implemented in Python 3.10. Human pre-label: No.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="30" customHeight="1" s="16">
       <c r="A23" s="22" t="inlineStr">
@@ -1557,13 +1640,39 @@
           <t>022</t>
         </is>
       </c>
-      <c r="B23" s="26" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="26" t="n"/>
-      <c r="G23" s="26" t="n"/>
-      <c r="H23" s="26" t="n"/>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t>Pitch structural pattern matching with match and case for clearer branching over structured data.</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D23" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>44473</v>
+      </c>
+      <c r="F23" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0634/</t>
+        </is>
+      </c>
+      <c r="G23" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H23" s="26" t="inlineStr">
+        <is>
+          <t>PEP 634; implemented in Python 3.10. Human pre-label: Yes (expressiveness vs language surface area).</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="16">
       <c r="A24" s="22" t="inlineStr">
@@ -1571,13 +1680,39 @@
           <t>023</t>
         </is>
       </c>
-      <c r="B24" s="26" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
-      <c r="H24" s="26" t="n"/>
+      <c r="B24" s="26" t="inlineStr">
+        <is>
+          <t>Pitch fine-grained source locations so Python tracebacks can point to the expression that caused an error.</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D24" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E24" s="30" t="n">
+        <v>44858</v>
+      </c>
+      <c r="F24" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0657/</t>
+        </is>
+      </c>
+      <c r="G24" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H24" s="26" t="inlineStr">
+        <is>
+          <t>PEP 657; implemented in Python 3.11. Human pre-label: No.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="16">
       <c r="A25" s="22" t="inlineStr">
@@ -1585,13 +1720,39 @@
           <t>024</t>
         </is>
       </c>
-      <c r="B25" s="26" t="n"/>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="26" t="n"/>
-      <c r="G25" s="26" t="n"/>
-      <c r="H25" s="26" t="n"/>
+      <c r="B25" s="26" t="inlineStr">
+        <is>
+          <t>Pitch a typing construct that lets a method state it returns the same specific subtype as self.</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D25" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E25" s="30" t="n">
+        <v>44858</v>
+      </c>
+      <c r="F25" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0673/</t>
+        </is>
+      </c>
+      <c r="G25" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H25" s="26" t="inlineStr">
+        <is>
+          <t>PEP 673; implemented in Python 3.11. Human pre-label: No.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="16">
       <c r="A26" s="22" t="inlineStr">
@@ -1599,13 +1760,39 @@
           <t>025</t>
         </is>
       </c>
-      <c r="B26" s="26" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="26" t="n"/>
-      <c r="G26" s="26" t="n"/>
-      <c r="H26" s="26" t="n"/>
+      <c r="B26" s="26" t="inlineStr">
+        <is>
+          <t>Pitch a safe Python-level API for libraries to inspect and provide the low-level buffer protocol.</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D26" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>44992</v>
+      </c>
+      <c r="F26" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0688/</t>
+        </is>
+      </c>
+      <c r="G26" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H26" s="26" t="inlineStr">
+        <is>
+          <t>PEP 688; resolution dated 2023-03-07, implemented for Python 3.12. Human pre-label: Yes (API power vs compatibility complexity).</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="16">
       <c r="A27" s="22" t="inlineStr">
@@ -1613,13 +1800,39 @@
           <t>026</t>
         </is>
       </c>
-      <c r="B27" s="26" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="26" t="n"/>
-      <c r="G27" s="26" t="n"/>
-      <c r="H27" s="26" t="n"/>
+      <c r="B27" s="26" t="inlineStr">
+        <is>
+          <t>Pitch a new syntax for declaring type parameters directly in generic classes, functions, and aliases.</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D27" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E27" s="30" t="n">
+        <v>45201</v>
+      </c>
+      <c r="F27" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0695/</t>
+        </is>
+      </c>
+      <c r="G27" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H27" s="26" t="inlineStr">
+        <is>
+          <t>PEP 695; implemented in Python 3.12. Human pre-label: Yes (typing ergonomics vs added syntax).</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="16">
       <c r="A28" s="22" t="inlineStr">
@@ -1627,13 +1840,39 @@
           <t>027</t>
         </is>
       </c>
-      <c r="B28" s="26" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="26" t="n"/>
-      <c r="G28" s="26" t="n"/>
-      <c r="H28" s="26" t="n"/>
+      <c r="B28" s="26" t="inlineStr">
+        <is>
+          <t>Pitch a formally specified f-string grammar so f-strings can support nested expressions and behave consistently.</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D28" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E28" s="30" t="n">
+        <v>44999</v>
+      </c>
+      <c r="F28" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0701/</t>
+        </is>
+      </c>
+      <c r="G28" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" s="26" t="inlineStr">
+        <is>
+          <t>PEP 701; resolution dated 2023-03-14, implemented for Python 3.12. Human pre-label: Yes.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="16">
       <c r="A29" s="22" t="inlineStr">
@@ -1641,13 +1880,39 @@
           <t>028</t>
         </is>
       </c>
-      <c r="B29" s="26" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="26" t="n"/>
-      <c r="G29" s="26" t="n"/>
-      <c r="H29" s="26" t="n"/>
+      <c r="B29" s="26" t="inlineStr">
+        <is>
+          <t>Pitch making the global interpreter lock local to each interpreter so isolated interpreters can run in parallel.</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D29" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="n">
+        <v>45201</v>
+      </c>
+      <c r="F29" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0684/</t>
+        </is>
+      </c>
+      <c r="G29" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H29" s="26" t="inlineStr">
+        <is>
+          <t>PEP 684; implemented for Python 3.12. Human pre-label: Yes (parallelism gains vs runtime extension complexity).</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="16">
       <c r="A30" s="22" t="inlineStr">
@@ -1655,13 +1920,39 @@
           <t>029</t>
         </is>
       </c>
-      <c r="B30" s="26" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="26" t="n"/>
-      <c r="G30" s="26" t="n"/>
-      <c r="H30" s="26" t="n"/>
+      <c r="B30" s="26" t="inlineStr">
+        <is>
+          <t>Pitch immutable reference counts for selected Python objects to reduce lifetime coordination across interpreters.</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D30" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="n">
+        <v>44858</v>
+      </c>
+      <c r="F30" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0683/</t>
+        </is>
+      </c>
+      <c r="G30" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H30" s="26" t="inlineStr">
+        <is>
+          <t>PEP 683; implemented in Python 3.12. Human pre-label: Yes (runtime performance trade-offs).</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="16">
       <c r="A31" s="22" t="inlineStr">
@@ -1669,13 +1960,39 @@
           <t>030</t>
         </is>
       </c>
-      <c r="B31" s="26" t="n"/>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="26" t="n"/>
-      <c r="G31" s="26" t="n"/>
-      <c r="H31" s="26" t="n"/>
+      <c r="B31" s="26" t="inlineStr">
+        <is>
+          <t>Pitch lazy annotation evaluation so annotations can be resolved later while preserving forward references and typing flexibility.</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Tech-OSS</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>Adopted</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="n">
+        <v>45054</v>
+      </c>
+      <c r="F31" s="26" t="inlineStr">
+        <is>
+          <t>https://peps.python.org/pep-0649/</t>
+        </is>
+      </c>
+      <c r="G31" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" s="26" t="inlineStr">
+        <is>
+          <t>PEP 649; resolution dated 2023-05-08. Human pre-label: Yes (annotation semantics vs backward compatibility).</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="16">
       <c r="A32" s="22" t="inlineStr">
@@ -1683,13 +2000,39 @@
           <t>031</t>
         </is>
       </c>
-      <c r="B32" s="26" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
-      <c r="H32" s="26" t="n"/>
+      <c r="B32" s="26" t="inlineStr">
+        <is>
+          <t>Build a developer-first payment API that lets online businesses accept cards, bank payments, and wallets with minimal integration work.</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>Funded</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="n">
+        <v>40816</v>
+      </c>
+      <c r="F32" s="26" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2011/09/30/sequoia-backed-stripe-launches-to-disrupt-the-online-payments-industry-with-a-developer-friendly-platform/</t>
+        </is>
+      </c>
+      <c r="G32" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H32" s="26" t="inlineStr">
+        <is>
+          <t>Contemporaneous launch/funding coverage; Stripe had publicly launched after raising about $2M. Human pre-label: No.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="16">
       <c r="A33" s="22" t="inlineStr">
@@ -1697,13 +2040,39 @@
           <t>032</t>
         </is>
       </c>
-      <c r="B33" s="26" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="26" t="n"/>
-      <c r="G33" s="26" t="n"/>
-      <c r="H33" s="26" t="n"/>
+      <c r="B33" s="26" t="inlineStr">
+        <is>
+          <t>Build a browser-based collaborative design tool that lets users create and edit visual work without desktop software.</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Funded</t>
+        </is>
+      </c>
+      <c r="E33" s="30" t="n">
+        <v>41451</v>
+      </c>
+      <c r="F33" s="26" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2013/06/26/21-years-4-million-dollars/</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" s="26" t="inlineStr">
+        <is>
+          <t>TechCrunch reported Figma's $3.8M funding and browser-based product. Human pre-label: No.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="16">
       <c r="A34" s="22" t="inlineStr">
@@ -1711,13 +2080,39 @@
           <t>033</t>
         </is>
       </c>
-      <c r="B34" s="26" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
-      <c r="H34" s="26" t="n"/>
+      <c r="B34" s="26" t="inlineStr">
+        <is>
+          <t>Build an Indian online payment gateway focused on simplifying digital payments for businesses and developers.</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Funded</t>
+        </is>
+      </c>
+      <c r="E34" s="30" t="n">
+        <v>42304</v>
+      </c>
+      <c r="F34" s="26" t="inlineStr">
+        <is>
+          <t>https://razorpay.com/blog/?p=587</t>
+        </is>
+      </c>
+      <c r="G34" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" s="26" t="inlineStr">
+        <is>
+          <t>Razorpay announced a seed + Series A totaling $11.5M on 2015-10-27. Human pre-label: No.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="16">
       <c r="A35" s="22" t="inlineStr">
@@ -1725,13 +2120,39 @@
           <t>034</t>
         </is>
       </c>
-      <c r="B35" s="26" t="n"/>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="26" t="n"/>
-      <c r="G35" s="26" t="n"/>
-      <c r="H35" s="26" t="n"/>
+      <c r="B35" s="26" t="inlineStr">
+        <is>
+          <t>Build an IoT home-awareness system that combines smart sensors into a single consumer product.</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>Funded</t>
+        </is>
+      </c>
+      <c r="E35" s="30" t="n">
+        <v>42523</v>
+      </c>
+      <c r="F35" s="26" t="inlineStr">
+        <is>
+          <t>https://www.crowdfundinsider.com/2016/06/87008-kickstarter-success-notion-secures-3-2m-during-seed-round-led-by-xl-innovate/</t>
+        </is>
+      </c>
+      <c r="G35" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="26" t="inlineStr">
+        <is>
+          <t>PRNewswire reported Notion's $3.2M seed round for its smart-home sensor system. Human pre-label: Yes (hardware adoption vs complexity).</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="30" customHeight="1" s="16">
       <c r="A36" s="22" t="inlineStr">
@@ -1739,13 +2160,39 @@
           <t>035</t>
         </is>
       </c>
-      <c r="B36" s="26" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n"/>
-      <c r="H36" s="26" t="n"/>
+      <c r="B36" s="26" t="inlineStr">
+        <is>
+          <t>Build a B2B commerce marketplace that lets small retailers source products online from brands and suppliers.</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>Funded</t>
+        </is>
+      </c>
+      <c r="E36" s="30" t="n">
+        <v>42697</v>
+      </c>
+      <c r="F36" s="26" t="inlineStr">
+        <is>
+          <t>https://www.medianama.com/2016/11/223-udaan-raises-10m/</t>
+        </is>
+      </c>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" s="26" t="inlineStr">
+        <is>
+          <t>Economic Times reported Udaan's $10M funding and B2B commerce focus. Human pre-label: Yes (marketplace liquidity requirements).</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="30" customHeight="1" s="16">
       <c r="A37" s="22" t="inlineStr">
@@ -1753,13 +2200,39 @@
           <t>036</t>
         </is>
       </c>
-      <c r="B37" s="26" t="n"/>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="26" t="n"/>
-      <c r="E37" s="26" t="n"/>
-      <c r="F37" s="26" t="n"/>
-      <c r="G37" s="26" t="n"/>
-      <c r="H37" s="26" t="n"/>
+      <c r="B37" s="26" t="inlineStr">
+        <is>
+          <t>Build a travel marketplace for hotels and stays, using technology to aggregate supply and make booking easier in India.</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>42790</v>
+      </c>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>https://www.medianama.com/2017/02/223-stayzilla-shutdown/</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="26" t="inlineStr">
+        <is>
+          <t>Contemporaneous report: Stayzilla suspended operations and planned a reboot; later history treats the shutdown as a failure. Human pre-label: Yes.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="30" customHeight="1" s="16">
       <c r="A38" s="22" t="inlineStr">
@@ -1767,13 +2240,39 @@
           <t>037</t>
         </is>
       </c>
-      <c r="B38" s="26" t="n"/>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
-      <c r="H38" s="26" t="n"/>
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t>Build an on-demand grocery delivery service that lets households order essentials through a mobile app.</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D38" s="26" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E38" s="30" t="n">
+        <v>42485</v>
+      </c>
+      <c r="F38" s="26" t="inlineStr">
+        <is>
+          <t>https://yourstory.com/2016/04/peppertap-shutdown/</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="26" t="inlineStr">
+        <is>
+          <t>Contemporaneous coverage reported PepperTap shutting its main grocery business after failing to reach profitability. Human pre-label: Yes.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="30" customHeight="1" s="16">
       <c r="A39" s="22" t="inlineStr">
@@ -1781,13 +2280,39 @@
           <t>038</t>
         </is>
       </c>
-      <c r="B39" s="26" t="n"/>
-      <c r="C39" s="26" t="n"/>
-      <c r="D39" s="26" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="26" t="n"/>
-      <c r="G39" s="26" t="n"/>
-      <c r="H39" s="26" t="n"/>
+      <c r="B39" s="26" t="inlineStr">
+        <is>
+          <t>Build a managed marketplace for used cars with inspection, financing, and technology-enabled transactions.</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D39" s="26" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E39" s="30" t="n">
+        <v>42608</v>
+      </c>
+      <c r="F39" s="26" t="inlineStr">
+        <is>
+          <t>https://www.medianama.com/2016/08/223-gozoomo-shuts-down/</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="26" t="inlineStr">
+        <is>
+          <t>Contemporaneous report: GoZoomo shut down after finding its unit economics unsustainable. Human pre-label: Yes.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="30" customHeight="1" s="16">
       <c r="A40" s="22" t="inlineStr">
@@ -1795,13 +2320,39 @@
           <t>039</t>
         </is>
       </c>
-      <c r="B40" s="26" t="n"/>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
-      <c r="H40" s="26" t="n"/>
+      <c r="B40" s="26" t="inlineStr">
+        <is>
+          <t>Build a local-language social network for Indian internet users with short-form posts and community conversations.</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="inlineStr">
+        <is>
+          <t>Startup</t>
+        </is>
+      </c>
+      <c r="D40" s="26" t="inlineStr">
+        <is>
+          <t>Failed</t>
+        </is>
+      </c>
+      <c r="E40" s="30" t="n">
+        <v>45475</v>
+      </c>
+      <c r="F40" s="26" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/2024/07/02/indian-social-network-koo-to-shut-down</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" s="26" t="inlineStr">
+        <is>
+          <t>TechCrunch reported Koo shutting down after funding and acquisition efforts did not produce a transaction. Human pre-label: Yes.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="30" customHeight="1" s="16">
       <c r="A41" s="22" t="inlineStr">
@@ -1823,13 +2374,39 @@
           <t>041</t>
         </is>
       </c>
-      <c r="B42" s="26" t="n"/>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="n"/>
-      <c r="H42" s="26" t="n"/>
+      <c r="B42" s="26" t="inlineStr">
+        <is>
+          <t>Build a digital lender that uses technology and alternative data to expand access to personal financial products.</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D42" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E42" s="30" t="n">
+        <v>45712</v>
+      </c>
+      <c r="F42" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1818874/000181887425000016/sofi-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G42" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H42" s="26" t="inlineStr">
+        <is>
+          <t>SoFi 2024 Form 10-K: Lending segment contribution profit was $890.5M. Segment result, not consolidated GAAP net income.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="30" customHeight="1" s="16">
       <c r="A43" s="22" t="inlineStr">
@@ -1837,13 +2414,39 @@
           <t>042</t>
         </is>
       </c>
-      <c r="B43" s="26" t="n"/>
-      <c r="C43" s="26" t="n"/>
-      <c r="D43" s="26" t="n"/>
-      <c r="E43" s="26" t="n"/>
-      <c r="F43" s="26" t="n"/>
-      <c r="G43" s="26" t="n"/>
-      <c r="H43" s="26" t="n"/>
+      <c r="B43" s="26" t="inlineStr">
+        <is>
+          <t>Build a technology-led consumer credit platform that originates and services personal loans online.</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D43" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>45701</v>
+      </c>
+      <c r="F43" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1409970/000140997025000009/lc-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G43" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H43" s="26" t="inlineStr">
+        <is>
+          <t>LendingClub 2024 Form 10-K: net income was $51.33M and total net revenue was $787M.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="30" customHeight="1" s="16">
       <c r="A44" s="22" t="inlineStr">
@@ -1851,13 +2454,39 @@
           <t>043</t>
         </is>
       </c>
-      <c r="B44" s="26" t="n"/>
-      <c r="C44" s="26" t="n"/>
-      <c r="D44" s="26" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="26" t="n"/>
-      <c r="G44" s="26" t="n"/>
-      <c r="H44" s="26" t="n"/>
+      <c r="B44" s="26" t="inlineStr">
+        <is>
+          <t>Build an AI-powered lending marketplace that matches borrowers with banks using machine-learning credit models.</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D44" s="26" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="E44" s="30" t="n">
+        <v>45702</v>
+      </c>
+      <c r="F44" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1647639/000164763925000018/upst-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G44" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" s="26" t="inlineStr">
+        <is>
+          <t>Upstart 2024 Form 10-K: net loss was $128.6M. Human pre-label: Yes (AI underwriting scale vs credit-cycle risk).</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="30" customHeight="1" s="16">
       <c r="A45" s="22" t="inlineStr">
@@ -1865,13 +2494,39 @@
           <t>044</t>
         </is>
       </c>
-      <c r="B45" s="26" t="n"/>
-      <c r="C45" s="26" t="n"/>
-      <c r="D45" s="26" t="n"/>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="26" t="n"/>
-      <c r="G45" s="26" t="n"/>
-      <c r="H45" s="26" t="n"/>
+      <c r="B45" s="26" t="inlineStr">
+        <is>
+          <t>Build a technology-driven health insurance platform that sells and manages individual and small-group plans.</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D45" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E45" s="30" t="n">
+        <v>45708</v>
+      </c>
+      <c r="F45" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1568651/000156865125000008/oscr-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G45" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H45" s="26" t="inlineStr">
+        <is>
+          <t>Oscar Health 2024 Form 10-K: net income was $26.121M, compared with a 2023 loss.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="30" customHeight="1" s="16">
       <c r="A46" s="22" t="inlineStr">
@@ -1879,13 +2534,39 @@
           <t>045</t>
         </is>
       </c>
-      <c r="B46" s="26" t="n"/>
-      <c r="C46" s="26" t="n"/>
-      <c r="D46" s="26" t="n"/>
-      <c r="E46" s="26" t="n"/>
-      <c r="F46" s="26" t="n"/>
-      <c r="G46" s="26" t="n"/>
-      <c r="H46" s="26" t="n"/>
+      <c r="B46" s="26" t="inlineStr">
+        <is>
+          <t>Build a mobile-first auto insurer that uses telematics and direct digital distribution to price drivers.</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D46" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E46" s="30" t="n">
+        <v>45714</v>
+      </c>
+      <c r="F46" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1788882/000162828025008137/root-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G46" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" s="26" t="inlineStr">
+        <is>
+          <t>Root 2024 10-K: operating income $78.5M and net income $30.9M. Human pre-label: Yes (pricing/underwriting model dependence).</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="30" customHeight="1" s="16">
       <c r="A47" s="22" t="inlineStr">
@@ -1893,13 +2574,39 @@
           <t>046</t>
         </is>
       </c>
-      <c r="B47" s="26" t="n"/>
-      <c r="C47" s="26" t="n"/>
-      <c r="D47" s="26" t="n"/>
-      <c r="E47" s="26" t="n"/>
-      <c r="F47" s="26" t="n"/>
-      <c r="G47" s="26" t="n"/>
-      <c r="H47" s="26" t="n"/>
+      <c r="B47" s="26" t="inlineStr">
+        <is>
+          <t>Build a regulated crypto exchange and financial platform for buying, selling, storing, and using digital assets.</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D47" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E47" s="30" t="n">
+        <v>45701</v>
+      </c>
+      <c r="F47" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1679788/000167978825000022/coin-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G47" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" s="26" t="inlineStr">
+        <is>
+          <t>Coinbase 2024 10-K: net income was $2.579B. Human pre-label: Yes (high regulatory and market-cycle exposure).</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="30" customHeight="1" s="16">
       <c r="A48" s="22" t="inlineStr">
@@ -1907,13 +2614,39 @@
           <t>047</t>
         </is>
       </c>
-      <c r="B48" s="26" t="n"/>
-      <c r="C48" s="26" t="n"/>
-      <c r="D48" s="26" t="n"/>
-      <c r="E48" s="26" t="n"/>
-      <c r="F48" s="26" t="n"/>
-      <c r="G48" s="26" t="n"/>
-      <c r="H48" s="26" t="n"/>
+      <c r="B48" s="26" t="inlineStr">
+        <is>
+          <t>Build a global digital payments platform that lets consumers and merchants move money online across markets.</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E48" s="30" t="n">
+        <v>45692</v>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1633917/000163391725000019/pypl-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H48" s="26" t="inlineStr">
+        <is>
+          <t>PayPal 2024 10-K: net income was $4.147B.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="30" customHeight="1" s="16">
       <c r="A49" s="22" t="inlineStr">
@@ -1921,13 +2654,39 @@
           <t>048</t>
         </is>
       </c>
-      <c r="B49" s="26" t="n"/>
-      <c r="C49" s="26" t="n"/>
-      <c r="D49" s="26" t="n"/>
-      <c r="E49" s="26" t="n"/>
-      <c r="F49" s="26" t="n"/>
-      <c r="G49" s="26" t="n"/>
-      <c r="H49" s="26" t="n"/>
+      <c r="B49" s="26" t="inlineStr">
+        <is>
+          <t>Build a mobile investing and brokerage app that makes stocks, options, and related financial products accessible to retail users.</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D49" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E49" s="30" t="n">
+        <v>45706</v>
+      </c>
+      <c r="F49" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1783879/000178387925000049/hood-20241231.htm</t>
+        </is>
+      </c>
+      <c r="G49" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" s="26" t="inlineStr">
+        <is>
+          <t>Robinhood 2024 10-K: net income was $1.411B. Human pre-label: Yes (retail-volume and market-cycle exposure).</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="30" customHeight="1" s="16">
       <c r="A50" s="22" t="inlineStr">
@@ -1935,13 +2694,39 @@
           <t>049</t>
         </is>
       </c>
-      <c r="B50" s="26" t="n"/>
-      <c r="C50" s="26" t="n"/>
-      <c r="D50" s="26" t="n"/>
-      <c r="E50" s="26" t="n"/>
-      <c r="F50" s="26" t="n"/>
-      <c r="G50" s="26" t="n"/>
-      <c r="H50" s="26" t="n"/>
+      <c r="B50" s="26" t="inlineStr">
+        <is>
+          <t>Build a low-cost international money-transfer product with a transparent exchange-rate and fee model.</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D50" s="26" t="inlineStr">
+        <is>
+          <t>Profitable</t>
+        </is>
+      </c>
+      <c r="E50" s="30" t="n">
+        <v>45485</v>
+      </c>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>https://www.investegate.co.uk/announcement/rns/wise-class-a--wise/wise-plc-preliminary-results-fy-end-31-march-2024/8256893</t>
+        </is>
+      </c>
+      <c r="G50" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H50" s="26" t="inlineStr">
+        <is>
+          <t>Wise FY2024 annual report: operating profit £501.9M and profit for the year £354.6M; annual report published in July 2024.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="30" customHeight="1" s="16">
       <c r="A51" s="22" t="inlineStr">
@@ -1949,13 +2734,39 @@
           <t>050</t>
         </is>
       </c>
-      <c r="B51" s="26" t="n"/>
-      <c r="C51" s="26" t="n"/>
-      <c r="D51" s="26" t="n"/>
-      <c r="E51" s="26" t="n"/>
-      <c r="F51" s="26" t="n"/>
-      <c r="G51" s="26" t="n"/>
-      <c r="H51" s="26" t="n"/>
+      <c r="B51" s="26" t="inlineStr">
+        <is>
+          <t>Build a consumer buy-now-pay-later product that underwrites purchases instantly and lets customers repay over time.</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="inlineStr">
+        <is>
+          <t>Financial-Product</t>
+        </is>
+      </c>
+      <c r="D51" s="26" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="E51" s="30" t="n">
+        <v>45590</v>
+      </c>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/Archives/edgar/data/1820953/000182095324000049/afrm-20241025.htm</t>
+        </is>
+      </c>
+      <c r="G51" s="26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" s="26" t="inlineStr">
+        <is>
+          <t>Affirm FY2024 filing materials: total revenue about $2.3B, operating loss $615.8M and net loss $517.8M.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="3">
